--- a/application/Documentation/Document.xlsx
+++ b/application/Documentation/Document.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Icoach-app\application\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{271F99EA-483A-4F22-AAB7-EAF134B724B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30F4A194-819A-47AA-B13F-200F1CA60035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,9 +54,6 @@
     <t>Step back to show full body</t>
   </si>
   <si>
-    <t>step_back.mp3</t>
-  </si>
-  <si>
     <t>SETUP_STAND_STRAIGHT</t>
   </si>
   <si>
@@ -66,9 +63,6 @@
     <t>Stand straight &amp; hold still</t>
   </si>
   <si>
-    <t>stand_straight.mp3</t>
-  </si>
-  <si>
     <t>SETUP_HOLD_{N}</t>
   </si>
   <si>
@@ -78,9 +72,6 @@
     <t>Hold Still... {N}</t>
   </si>
   <si>
-    <t>beep.mp3</t>
-  </si>
-  <si>
     <t>SYSTEM_READY_GO</t>
   </si>
   <si>
@@ -90,9 +81,6 @@
     <t>GO!</t>
   </si>
   <si>
-    <t>start.mp3</t>
-  </si>
-  <si>
     <t>CMD_GO_DOWN</t>
   </si>
   <si>
@@ -102,9 +90,6 @@
     <t>Go Down</t>
   </si>
   <si>
-    <t>go_down.mp3</t>
-  </si>
-  <si>
     <t>FIX_LOWER_HIPS</t>
   </si>
   <si>
@@ -114,9 +99,6 @@
     <t>Lower your hips more</t>
   </si>
   <si>
-    <t>lower_hips.mp3</t>
-  </si>
-  <si>
     <t>REP_SUCCESS</t>
   </si>
   <si>
@@ -126,9 +108,6 @@
     <t>Perfect!</t>
   </si>
   <si>
-    <t>count_rep.mp3</t>
-  </si>
-  <si>
     <t>Superman</t>
   </si>
   <si>
@@ -141,9 +120,6 @@
     <t>Lie on your stomach</t>
   </si>
   <si>
-    <t>lie_stomach.mp3</t>
-  </si>
-  <si>
     <t>Setup complete</t>
   </si>
   <si>
@@ -159,9 +135,6 @@
     <t>Fly Up (Arms &amp; Legs)</t>
   </si>
   <si>
-    <t>fly_up.mp3</t>
-  </si>
-  <si>
     <t>HOLD_STABILIZE</t>
   </si>
   <si>
@@ -171,9 +144,6 @@
     <t>Hold...</t>
   </si>
   <si>
-    <t>hold.mp3</t>
-  </si>
-  <si>
     <t>ERR_LIFT_LEGS</t>
   </si>
   <si>
@@ -183,9 +153,6 @@
     <t>Lift your legs too</t>
   </si>
   <si>
-    <t>lift_legs.mp3</t>
-  </si>
-  <si>
     <t>ERR_LIFT_ARMS</t>
   </si>
   <si>
@@ -195,9 +162,6 @@
     <t>Lift your arms too</t>
   </si>
   <si>
-    <t>lift_arms.mp3</t>
-  </si>
-  <si>
     <t>ERR_RESET_FULL</t>
   </si>
   <si>
@@ -207,9 +171,6 @@
     <t>Rest fully on the floor</t>
   </si>
   <si>
-    <t>reset_down.mp3</t>
-  </si>
-  <si>
     <t>Rep completed (held for 0.3s)</t>
   </si>
   <si>
@@ -228,9 +189,6 @@
     <t>Lie on your back</t>
   </si>
   <si>
-    <t>lie_back.mp3</t>
-  </si>
-  <si>
     <t>ERR_BENT_KNEES</t>
   </si>
   <si>
@@ -240,9 +198,6 @@
     <t>Straighten your legs</t>
   </si>
   <si>
-    <t>straighten_legs.mp3</t>
-  </si>
-  <si>
     <t>ERR_LEGS_SYNC</t>
   </si>
   <si>
@@ -252,9 +207,6 @@
     <t>Keep feet together</t>
   </si>
   <si>
-    <t>feet_together.mp3</t>
-  </si>
-  <si>
     <t>CMD_RAISE_LEGS</t>
   </si>
   <si>
@@ -264,9 +216,6 @@
     <t>Raise your legs</t>
   </si>
   <si>
-    <t>raise_legs.mp3</t>
-  </si>
-  <si>
     <t>CMD_LOWER_SLOWLY</t>
   </si>
   <si>
@@ -276,9 +225,6 @@
     <t>Lower slowly</t>
   </si>
   <si>
-    <t>lower_slow.mp3</t>
-  </si>
-  <si>
     <t>Good!</t>
   </si>
   <si>
@@ -294,9 +240,6 @@
     <t>Get into plank position</t>
   </si>
   <si>
-    <t>setup_plank.mp3</t>
-  </si>
-  <si>
     <t>ERR_HIPS_TOO_LOW</t>
   </si>
   <si>
@@ -306,9 +249,6 @@
     <t>Raise your hips</t>
   </si>
   <si>
-    <t>hips_up.mp3</t>
-  </si>
-  <si>
     <t>ERR_HIPS_TOO_HIGH</t>
   </si>
   <si>
@@ -318,9 +258,6 @@
     <t>Lower your hips</t>
   </si>
   <si>
-    <t>hips_down.mp3</t>
-  </si>
-  <si>
     <t>ERR_BENT_ELBOWS</t>
   </si>
   <si>
@@ -330,9 +267,6 @@
     <t>Straighten your arms</t>
   </si>
   <si>
-    <t>straighten_arms.mp3</t>
-  </si>
-  <si>
     <t>ERR_KNEES_TOUCHING</t>
   </si>
   <si>
@@ -342,9 +276,6 @@
     <t>Knees off the floor</t>
   </si>
   <si>
-    <t>knees_up.mp3</t>
-  </si>
-  <si>
     <t>HOLD_FIXED</t>
   </si>
   <si>
@@ -354,9 +285,6 @@
     <t>Hold steady...</t>
   </si>
   <si>
-    <t>ticking.mp3</t>
-  </si>
-  <si>
     <t>Elbow Plank</t>
   </si>
   <si>
@@ -369,9 +297,6 @@
     <t>Rest on your elbows</t>
   </si>
   <si>
-    <t>elbows_down.mp3</t>
-  </si>
-  <si>
     <t>Hips sagging</t>
   </si>
   <si>
@@ -384,9 +309,6 @@
     <t>Straighten your back</t>
   </si>
   <si>
-    <t>fix_back.mp3</t>
-  </si>
-  <si>
     <t>Crunch</t>
   </si>
   <si>
@@ -399,9 +321,6 @@
     <t>Bend your knees</t>
   </si>
   <si>
-    <t>bend_knees.mp3</t>
-  </si>
-  <si>
     <t>Feet are too far apart</t>
   </si>
   <si>
@@ -417,18 +336,12 @@
     <t>Keep hands behind head</t>
   </si>
   <si>
-    <t>hands_back.mp3</t>
-  </si>
-  <si>
     <t>User on floor</t>
   </si>
   <si>
     <t>Crunch Up</t>
   </si>
   <si>
-    <t>crunch_up.mp3</t>
-  </si>
-  <si>
     <t>User is up</t>
   </si>
   <si>
@@ -447,18 +360,12 @@
     <t>Adjust posture / Camera</t>
   </si>
   <si>
-    <t>adjust_camera.mp3</t>
-  </si>
-  <si>
     <t>Standing straight, ready</t>
   </si>
   <si>
     <t>Ready... Jump!</t>
   </si>
   <si>
-    <t>start_jump.mp3</t>
-  </si>
-  <si>
     <t>CMD_JUMP_OPEN</t>
   </si>
   <si>
@@ -468,9 +375,6 @@
     <t>Jump &amp; Open!</t>
   </si>
   <si>
-    <t>jump_open.mp3</t>
-  </si>
-  <si>
     <t>CMD_JUMP_CLOSE</t>
   </si>
   <si>
@@ -480,9 +384,6 @@
     <t>Jump &amp; Close!</t>
   </si>
   <si>
-    <t>jump_close.mp3</t>
-  </si>
-  <si>
     <t>ERR_LEGS_WIDTH</t>
   </si>
   <si>
@@ -492,9 +393,6 @@
     <t>Wider legs!</t>
   </si>
   <si>
-    <t>wider_legs.mp3</t>
-  </si>
-  <si>
     <t>ERR_ARMS_LAZY</t>
   </si>
   <si>
@@ -504,9 +402,6 @@
     <t>Arms higher!</t>
   </si>
   <si>
-    <t>arms_higher.mp3</t>
-  </si>
-  <si>
     <t>Full cycle completed</t>
   </si>
   <si>
@@ -522,9 +417,6 @@
     <t>Step back for arm clearance</t>
   </si>
   <si>
-    <t>"Step back"</t>
-  </si>
-  <si>
     <t>CMD_RAISE_ARMS</t>
   </si>
   <si>
@@ -534,18 +426,12 @@
     <t>Raise arms sideways</t>
   </si>
   <si>
-    <t>"Arms up"</t>
-  </si>
-  <si>
     <t>STRAIGHTEN_ARMS</t>
   </si>
   <si>
     <t>Elbow angle &lt; 155°</t>
   </si>
   <si>
-    <t>"Straighten arms"</t>
-  </si>
-  <si>
     <t>ERR_TOO_HIGH</t>
   </si>
   <si>
@@ -555,9 +441,6 @@
     <t>Don't go above shoulders</t>
   </si>
   <si>
-    <t>"Too high"</t>
-  </si>
-  <si>
     <t>PERFECT</t>
   </si>
   <si>
@@ -567,18 +450,12 @@
     <t>Perfect Level</t>
   </si>
   <si>
-    <t>"Hold"</t>
-  </si>
-  <si>
     <t>Controlled movement</t>
   </si>
   <si>
     <t>Excellent Rep!</t>
   </si>
   <si>
-    <t>"Good"</t>
-  </si>
-  <si>
     <t>Front Raises</t>
   </si>
   <si>
@@ -588,9 +465,6 @@
     <t>Adjust position, show arms</t>
   </si>
   <si>
-    <t>"Show arms"</t>
-  </si>
-  <si>
     <t>CMD_RAISE_FRONT</t>
   </si>
   <si>
@@ -600,9 +474,6 @@
     <t>Raise arms in front</t>
   </si>
   <si>
-    <t>"Raise front"</t>
-  </si>
-  <si>
     <t>RAISE_YOUR_ARM</t>
   </si>
   <si>
@@ -612,9 +483,6 @@
     <t>Raise higher to chest level</t>
   </si>
   <si>
-    <t>"Higher"</t>
-  </si>
-  <si>
     <t>ERR_SWINGING</t>
   </si>
   <si>
@@ -624,9 +492,6 @@
     <t>Keep your torso still</t>
   </si>
   <si>
-    <t>"Don't swing"</t>
-  </si>
-  <si>
     <t>GOOD_REP</t>
   </si>
   <si>
@@ -636,9 +501,6 @@
     <t>Good Control</t>
   </si>
   <si>
-    <t>"Nice"</t>
-  </si>
-  <si>
     <t>Rep counted</t>
   </si>
   <si>
@@ -651,9 +513,6 @@
     <t>Stand tall, weights at shoulders</t>
   </si>
   <si>
-    <t>"Stand tall"</t>
-  </si>
-  <si>
     <t>ERR_CAMERA_VIEW</t>
   </si>
   <si>
@@ -663,9 +522,6 @@
     <t>Arms must be visible overhead</t>
   </si>
   <si>
-    <t>"Fix camera"</t>
-  </si>
-  <si>
     <t>ERR_ARCHED_BACK</t>
   </si>
   <si>
@@ -675,9 +531,6 @@
     <t>Keep core tight, don't lean back</t>
   </si>
   <si>
-    <t>"Don't lean"</t>
-  </si>
-  <si>
     <t>ERR_LOW_ARMS</t>
   </si>
   <si>
@@ -687,9 +540,6 @@
     <t>Don't drop elbows too low</t>
   </si>
   <si>
-    <t>"Elbows up"</t>
-  </si>
-  <si>
     <t>PUSH_UP</t>
   </si>
   <si>
@@ -699,9 +549,6 @@
     <t>Press overhead</t>
   </si>
   <si>
-    <t>"Press up"</t>
-  </si>
-  <si>
     <t>LOWER_SLOWLY</t>
   </si>
   <si>
@@ -711,16 +558,169 @@
     <t>Lower firmly to shoulders</t>
   </si>
   <si>
-    <t>"Lower"</t>
-  </si>
-  <si>
     <t>Returned to start</t>
   </si>
   <si>
     <t>Great lift!</t>
   </si>
   <si>
-    <t>"Great"</t>
+    <t>step_back</t>
+  </si>
+  <si>
+    <t>stand_straight</t>
+  </si>
+  <si>
+    <t>beep</t>
+  </si>
+  <si>
+    <t>start</t>
+  </si>
+  <si>
+    <t>go_down</t>
+  </si>
+  <si>
+    <t>lower_hips</t>
+  </si>
+  <si>
+    <t>count_rep</t>
+  </si>
+  <si>
+    <t>lie_stomach</t>
+  </si>
+  <si>
+    <t>fly_up</t>
+  </si>
+  <si>
+    <t>hold</t>
+  </si>
+  <si>
+    <t>lift_legs</t>
+  </si>
+  <si>
+    <t>lift_arms</t>
+  </si>
+  <si>
+    <t>reset_down</t>
+  </si>
+  <si>
+    <t>lie_back</t>
+  </si>
+  <si>
+    <t>straighten_legs</t>
+  </si>
+  <si>
+    <t>feet_together</t>
+  </si>
+  <si>
+    <t>raise_legs</t>
+  </si>
+  <si>
+    <t>lower_slow</t>
+  </si>
+  <si>
+    <t>setup_plank</t>
+  </si>
+  <si>
+    <t>hips_up</t>
+  </si>
+  <si>
+    <t>hips_down</t>
+  </si>
+  <si>
+    <t>straighten_arms</t>
+  </si>
+  <si>
+    <t>knees_up</t>
+  </si>
+  <si>
+    <t>ticking</t>
+  </si>
+  <si>
+    <t>elbows_down</t>
+  </si>
+  <si>
+    <t>fix_back</t>
+  </si>
+  <si>
+    <t>bend_knees</t>
+  </si>
+  <si>
+    <t>hands_back</t>
+  </si>
+  <si>
+    <t>crunch_up</t>
+  </si>
+  <si>
+    <t>adjust_camera</t>
+  </si>
+  <si>
+    <t>start_jump</t>
+  </si>
+  <si>
+    <t>jump_open</t>
+  </si>
+  <si>
+    <t>jump_close</t>
+  </si>
+  <si>
+    <t>wider_legs</t>
+  </si>
+  <si>
+    <t>arms_higher</t>
+  </si>
+  <si>
+    <t>Step back</t>
+  </si>
+  <si>
+    <t>Arms up</t>
+  </si>
+  <si>
+    <t>Straighten arms</t>
+  </si>
+  <si>
+    <t>Too high</t>
+  </si>
+  <si>
+    <t>Hold</t>
+  </si>
+  <si>
+    <t>Good</t>
+  </si>
+  <si>
+    <t>Show arms</t>
+  </si>
+  <si>
+    <t>Raise front</t>
+  </si>
+  <si>
+    <t>Higher</t>
+  </si>
+  <si>
+    <t>Don't swing</t>
+  </si>
+  <si>
+    <t>Nice</t>
+  </si>
+  <si>
+    <t>Stand tall</t>
+  </si>
+  <si>
+    <t>Fix camera</t>
+  </si>
+  <si>
+    <t>Don't lean</t>
+  </si>
+  <si>
+    <t>Elbows up</t>
+  </si>
+  <si>
+    <t>Press up</t>
+  </si>
+  <si>
+    <t>Lower</t>
+  </si>
+  <si>
+    <t>Great</t>
   </si>
 </sst>
 </file>
@@ -1201,7 +1201,7 @@
         <v>8</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>9</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1209,16 +1209,16 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="E3" s="1" t="s">
-        <v>13</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1226,16 +1226,16 @@
         <v>5</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>17</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1243,16 +1243,16 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>21</v>
+        <v>182</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1260,16 +1260,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>25</v>
+        <v>183</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1277,16 +1277,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>29</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1294,1016 +1294,1016 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>33</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>38</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>21</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="D11" s="1" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>44</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>48</v>
+        <v>188</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>52</v>
+        <v>189</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>56</v>
+        <v>190</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>60</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>33</v>
+        <v>185</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>67</v>
+        <v>192</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>71</v>
+        <v>193</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>75</v>
+        <v>194</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>79</v>
+        <v>195</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>80</v>
-      </c>
       <c r="C21" s="1" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>83</v>
+        <v>196</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>33</v>
+        <v>185</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>89</v>
+        <v>197</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>93</v>
+        <v>198</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>97</v>
+        <v>199</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>101</v>
+        <v>200</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>105</v>
+        <v>201</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="E28" s="1" t="s">
-        <v>109</v>
+        <v>202</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>89</v>
+        <v>197</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>114</v>
+        <v>203</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>115</v>
-      </c>
       <c r="D31" s="1" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>93</v>
+        <v>198</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>117</v>
+        <v>92</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>119</v>
+        <v>204</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>105</v>
+        <v>201</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>109</v>
+        <v>202</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>67</v>
+        <v>192</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>124</v>
+        <v>205</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>126</v>
+        <v>99</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>75</v>
+        <v>194</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>128</v>
+        <v>101</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>130</v>
+        <v>206</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>133</v>
+        <v>207</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>134</v>
+        <v>105</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>25</v>
+        <v>183</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>33</v>
+        <v>185</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>137</v>
+        <v>108</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>138</v>
+        <v>109</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>140</v>
+        <v>208</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>141</v>
+        <v>111</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>142</v>
+        <v>112</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>143</v>
+        <v>209</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>144</v>
+        <v>113</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>146</v>
+        <v>115</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>147</v>
+        <v>210</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>148</v>
+        <v>116</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>149</v>
+        <v>117</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>151</v>
+        <v>211</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>152</v>
+        <v>119</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>154</v>
+        <v>121</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>155</v>
+        <v>212</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>156</v>
+        <v>122</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>157</v>
+        <v>123</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>158</v>
+        <v>124</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>159</v>
+        <v>213</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>33</v>
+        <v>185</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>162</v>
+        <v>127</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>163</v>
+        <v>128</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>164</v>
+        <v>129</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>165</v>
+        <v>214</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>162</v>
+        <v>127</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>166</v>
+        <v>130</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>167</v>
+        <v>131</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>168</v>
+        <v>132</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>169</v>
+        <v>215</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>162</v>
+        <v>127</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>170</v>
+        <v>133</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>172</v>
+        <v>216</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>162</v>
+        <v>127</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>173</v>
+        <v>135</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>174</v>
+        <v>136</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>175</v>
+        <v>137</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>176</v>
+        <v>217</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>162</v>
+        <v>127</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>177</v>
+        <v>138</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>178</v>
+        <v>139</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>180</v>
+        <v>218</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>162</v>
+        <v>127</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>181</v>
+        <v>141</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>182</v>
+        <v>142</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>183</v>
+        <v>219</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>184</v>
+        <v>143</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>185</v>
+        <v>144</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>186</v>
+        <v>145</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>187</v>
+        <v>220</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>184</v>
+        <v>143</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>188</v>
+        <v>146</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>189</v>
+        <v>147</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>190</v>
+        <v>148</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>191</v>
+        <v>221</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>184</v>
+        <v>143</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>192</v>
+        <v>149</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>193</v>
+        <v>150</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>194</v>
+        <v>151</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>195</v>
+        <v>222</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>184</v>
+        <v>143</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>196</v>
+        <v>152</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>197</v>
+        <v>153</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>198</v>
+        <v>154</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>199</v>
+        <v>223</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>184</v>
+        <v>143</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>200</v>
+        <v>155</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>201</v>
+        <v>156</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>202</v>
+        <v>157</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>184</v>
+        <v>143</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>204</v>
+        <v>158</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>205</v>
+        <v>159</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>183</v>
+        <v>219</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>206</v>
+        <v>160</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>207</v>
+        <v>161</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>206</v>
+        <v>160</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>209</v>
+        <v>162</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>210</v>
+        <v>163</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>211</v>
+        <v>164</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>206</v>
+        <v>160</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>213</v>
+        <v>165</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>214</v>
+        <v>166</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>215</v>
+        <v>167</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>206</v>
+        <v>160</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>217</v>
+        <v>168</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>218</v>
+        <v>169</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>219</v>
+        <v>170</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>206</v>
+        <v>160</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>221</v>
+        <v>171</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>222</v>
+        <v>172</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>223</v>
+        <v>173</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>206</v>
+        <v>160</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>225</v>
+        <v>174</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>226</v>
+        <v>175</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>227</v>
+        <v>176</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>206</v>
+        <v>160</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>200</v>
+        <v>155</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>229</v>
+        <v>177</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>231</v>
